--- a/FASE 1/Cálculo de Aderência.xlsx
+++ b/FASE 1/Cálculo de Aderência.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucpredu-my.sharepoint.com/personal/stefany_oliveira_pucpr_edu_br/Documents/Documentos/GitHub/PROJETO-EXPERIENCIA-CRIATIVA-INOVANDO-EM-PROCESSOS/FASE 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E5F1155B-384C-451C-871D-3630B7CFA6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{E5F1155B-384C-451C-871D-3630B7CFA6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D096CF9-D2DC-4F80-AAEE-1D55475FF62B}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2BA9A6CF-492F-4CCB-A27F-FFC55E200CD8}"/>
+    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{2BA9A6CF-492F-4CCB-A27F-FFC55E200CD8}"/>
   </bookViews>
   <sheets>
     <sheet name="Planejamento da Entrevista" sheetId="1" r:id="rId1"/>
@@ -1564,10 +1564,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>38</c:v>
+                  <c:v>37</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>31</c:v>
+                  <c:v>32</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3309,10 +3309,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>2</c:v>
+                  <c:v>1</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>4</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11681,6 +11681,10 @@
 </FeaturePropertyBags>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
   <a:themeElements>
@@ -12922,7 +12926,7 @@
         <v>89</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
@@ -12990,15 +12994,15 @@
       </c>
       <c r="B90" s="3">
         <f>COUNTIFS($C$84:$C$88, "Atende*")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C90" s="3">
         <f>COUNTIFS($C$84:$C$88, "Não atende*")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D90" s="9">
         <f>(B90/A90)</f>
-        <v>0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
@@ -13108,7 +13112,6 @@
         <v>6</v>
       </c>
       <c r="B101" s="3">
-        <f>COUNTIFS($C$94:$C$99, "Atende*")</f>
         <v>3</v>
       </c>
       <c r="C101" s="3">
@@ -13448,15 +13451,15 @@
       </c>
       <c r="B134" s="3">
         <f>COUNTIFS($C$3:$C$126, "Atende*")</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C134" s="3">
         <f>COUNTIFS($C$3:$C$126, "Não atende*")</f>
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D134" s="6">
         <f>(B134/A134)</f>
-        <v>0.55072463768115942</v>
+        <v>0.53623188405797106</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
@@ -13590,15 +13593,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101002854D116ED16784B832F80E0BEF72847" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="1a01681b81d4cac73bfcf1764dfdca6d">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d4c4f424-04dc-4067-abf7-2cdaf5be40b7" xmlns:ns4="59a2b59b-6ce1-4938-bf5c-70297f05899c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="32e5ae574255e8b6d7cb0b625cde7ee3" ns3:_="" ns4:_="">
     <xsd:import namespace="d4c4f424-04dc-4067-abf7-2cdaf5be40b7"/>
@@ -13831,32 +13825,33 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{924656E7-7DAC-4850-9A06-F6B76FD8F491}">
   <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="59a2b59b-6ce1-4938-bf5c-70297f05899c"/>
+    <ds:schemaRef ds:uri="d4c4f424-04dc-4067-abf7-2cdaf5be40b7"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="d4c4f424-04dc-4067-abf7-2cdaf5be40b7"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="59a2b59b-6ce1-4938-bf5c-70297f05899c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF95609E-6CCE-44D6-BD6A-38C9BFA1C94E}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{710113E9-F6C8-4C98-88F2-4A67A0E932F7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -13875,6 +13870,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BF95609E-6CCE-44D6-BD6A-38C9BFA1C94E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{8a1ef6c3-8324-4103-bf4a-1328c5dc3653}" enabled="0" method="" siteId="{8a1ef6c3-8324-4103-bf4a-1328c5dc3653}" removed="1"/>

--- a/FASE 1/Cálculo de Aderência.xlsx
+++ b/FASE 1/Cálculo de Aderência.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pucpredu-my.sharepoint.com/personal/stefany_oliveira_pucpr_edu_br/Documents/Documentos/GitHub/PROJETO-EXPERIENCIA-CRIATIVA-INOVANDO-EM-PROCESSOS/FASE 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{E5F1155B-384C-451C-871D-3630B7CFA6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3D096CF9-D2DC-4F80-AAEE-1D55475FF62B}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{E5F1155B-384C-451C-871D-3630B7CFA6F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCE90F07-EB57-4A06-897C-D4B2A47DE258}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="12852" windowWidth="23256" windowHeight="12456" xr2:uid="{2BA9A6CF-492F-4CCB-A27F-FFC55E200CD8}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{2BA9A6CF-492F-4CCB-A27F-FFC55E200CD8}"/>
   </bookViews>
   <sheets>
     <sheet name="Planejamento da Entrevista" sheetId="1" r:id="rId1"/>
@@ -1564,10 +1564,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>37</c:v>
+                  <c:v>39</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>32</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2831,10 +2831,10 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
-                  <c:v>0</c:v>
+                  <c:v>2</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>5</c:v>
+                  <c:v>3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -12732,7 +12732,7 @@
         <v>71</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -12754,7 +12754,7 @@
         <v>73</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12789,15 +12789,15 @@
       </c>
       <c r="B71" s="3">
         <f>COUNTIFS($C$65:$C$69, "Atende*")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C71" s="3">
         <f>COUNTIFS($C$65:$C$69, "Não atende*")</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D71" s="9">
         <f>(B71/A71)</f>
-        <v>0</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
@@ -13451,15 +13451,15 @@
       </c>
       <c r="B134" s="3">
         <f>COUNTIFS($C$3:$C$126, "Atende*")</f>
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C134" s="3">
         <f>COUNTIFS($C$3:$C$126, "Não atende*")</f>
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D134" s="6">
         <f>(B134/A134)</f>
-        <v>0.53623188405797106</v>
+        <v>0.56521739130434778</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
